--- a/calibration/Watbal2026_three_site_calibration_summary.xlsx
+++ b/calibration/Watbal2026_three_site_calibration_summary.xlsx
@@ -9,9 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Fit statistics" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Crop &amp; soil water" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Cross-site findings" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Original vs optimised" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Fit statistics" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Crop &amp; soil water" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Cross-site findings" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -98,6 +99,64 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="C28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Calibration code only; not in the vege file.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">David's earlier practice: CN 86 tilled, 90 zero till via a separate soil file (not checked here).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Not physical: optimiser used evaporation to offset crop over-use of water.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Not physical: optimiser used evaporation to offset crop over-use of water.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
     <comment ref="J5" authorId="0">
       <text>
         <r>
@@ -127,7 +186,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="122">
   <si>
     <t xml:space="preserve">Watbal2026 optimised parameters — three catchment sites (Oct 2026)</t>
   </si>
@@ -246,6 +305,126 @@
     <t xml:space="preserve">Fallow weeds at Wallumbilla are in the calibration wrapper only.</t>
   </si>
   <si>
+    <t xml:space="preserve">Original (soil and vege file) vs optimised parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original = values in each site's soil and vege files before calibration. Optimised = Oct 2026 Watbal2026 pooled fits. Blue = optimised or adopted value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallumbilla original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallumbilla optimised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenwood original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenwood optimised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenmount original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenmount optimised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUNOFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">separate soil (~90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMC form</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uncapped (HowLeaky)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uncapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soil cracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOIL EVAPORATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRAINAGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (not fitted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EROSION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exponential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.40 (not fitted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observed 0.14 / 0.20 / 0.21 / 0.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">observed 0.11 / 0.11 / 0.08 / 0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROP (WHEAT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No-stress PAW fraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (not fitted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 (not fitted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">file vege</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slower roots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenwood schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original CN2 used the capped AMC form; optimised CN2 uses the uncapped HowLeaky form, which needs a higher CN2 for the same runoff. At typical wetness the optimised 90–94 gives an effective bare-soil CN of about 78–83.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At Wallumbilla K and delivery ratio act together: with the delivery ratio held at 0.4, K fell from 0.40 to 0.149, so the original file over-predicted suspended sediment about 2.7 times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenwood and Greenmount were fitted to total soil movement, so no delivery ratio was used; the values shown are observed suspended ÷ soil movement (Burnt / Incorporated / Mulch / Zero till).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenmount values come from the fit made before the Mulch soil-movement correction (corrections.csv); the sediment parameters will shift slightly on refit.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fit statistics by treatment</t>
   </si>
   <si>
@@ -289,9 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tilled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
   </si>
   <si>
     <t xml:space="preserve">Min till</t>
@@ -452,7 +628,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,7 +638,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE5EE"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFDDE5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -509,11 +691,43 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -522,47 +736,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -586,7 +808,7 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
@@ -829,304 +1051,304 @@
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>92.2</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>93.6</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>90.2</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>15.1</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>14.2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>5.4</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>0.095</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>0.057</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.149</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>0.62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>0.015</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>0.31</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>3.33</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>5.1</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>6.96</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>0.14</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>33.4</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>0.037</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="8" t="n">
         <v>0.06</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1147,490 +1369,566 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="8" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="8" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>93.6</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="E8" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="B9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="C9" s="15" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="D9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="F9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="C10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>426.9</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>426.9</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">IFERROR(D7/C7,"")</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="C12" s="15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E19" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>193.7</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>193.7</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <f aca="false">IFERROR(I7/H7,"")</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="L7" s="12" t="n">
+      <c r="F19" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>355.6</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>362.2</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <f aca="false">IFERROR(D8/C8,"")</f>
-        <v>1.0185601799775</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="J8" s="11" t="n">
-        <f aca="false">IFERROR(I8/H8,"")</f>
-        <v>1.23353293413174</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>300.5</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>297.5</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <f aca="false">IFERROR(D9/C9,"")</f>
-        <v>0.990016638935108</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <f aca="false">IFERROR(I9/H9,"")</f>
-        <v>0.905737704918033</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L9" s="12" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>328.9</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>329.3</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <f aca="false">IFERROR(D10/C10,"")</f>
-        <v>1.00121617512922</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="J10" s="11" t="n">
-        <f aca="false">IFERROR(I10/H10,"")</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>818.6</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>818.5</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <f aca="false">IFERROR(D11/C11,"")</f>
-        <v>0.999877840215001</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>535.7</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>626.4</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <f aca="false">IFERROR(I11/H11,"")</f>
-        <v>1.16931118163151</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>654.1</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>656.2</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <f aca="false">IFERROR(D12/C12,"")</f>
-        <v>1.00321051826938</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>180.1</v>
-      </c>
-      <c r="J12" s="11" t="n">
-        <f aca="false">IFERROR(I12/H12,"")</f>
-        <v>0.983615510649918</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>557.9</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>540.6</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <f aca="false">IFERROR(D13/C13,"")</f>
-        <v>0.968990858576806</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>110</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <f aca="false">IFERROR(I13/H13,"")</f>
-        <v>0.786363636363636</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>424.9</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>424.9</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <f aca="false">IFERROR(D14/C14,"")</f>
-        <v>1</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" s="11" t="n">
-        <f aca="false">IFERROR(I14/H14,"")</f>
-        <v>1</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>63</v>
+      <c r="B26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1650,76 +1948,579 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>426.9</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>426.9</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <f aca="false">IFERROR(D7/C7,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <f aca="false">IFERROR(I7/H7,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L7" s="22" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <f aca="false">IFERROR(D8/C8,"")</f>
+        <v>1.0185601799775</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <f aca="false">IFERROR(I8/H8,"")</f>
+        <v>1.23353293413174</v>
+      </c>
+      <c r="K8" s="20" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="L8" s="22" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <f aca="false">IFERROR(D9/C9,"")</f>
+        <v>0.990016638935108</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I9" s="23" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <f aca="false">IFERROR(I9/H9,"")</f>
+        <v>0.905737704918033</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L9" s="22" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <f aca="false">IFERROR(D10/C10,"")</f>
+        <v>1.00121617512922</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I10" s="23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <f aca="false">IFERROR(I10/H10,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L10" s="22" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>818.6</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>818.5</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <f aca="false">IFERROR(D11/C11,"")</f>
+        <v>0.999877840215001</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>535.7</v>
+      </c>
+      <c r="I11" s="23" t="n">
+        <v>626.4</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <f aca="false">IFERROR(I11/H11,"")</f>
+        <v>1.16931118163151</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L11" s="22" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>654.1</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>656.2</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <f aca="false">IFERROR(D12/C12,"")</f>
+        <v>1.00321051826938</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="I12" s="23" t="n">
+        <v>180.1</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <f aca="false">IFERROR(I12/H12,"")</f>
+        <v>0.983615510649918</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>557.9</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>540.6</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <f aca="false">IFERROR(D13/C13,"")</f>
+        <v>0.968990858576806</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>110</v>
+      </c>
+      <c r="I13" s="23" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <f aca="false">IFERROR(I13/H13,"")</f>
+        <v>0.786363636363636</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L13" s="22" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>424.9</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>424.9</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <f aca="false">IFERROR(D14/C14,"")</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <f aca="false">IFERROR(I14/H14,"")</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L14" s="22" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>76</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +2534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1741,40 +2542,40 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>82</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
